--- a/data/raw/inventory/Week 19/Nexlev/Inventory Snapshot.xlsx
+++ b/data/raw/inventory/Week 19/Nexlev/Inventory Snapshot.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\inventory\Week 19\Nexlev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABA4DA19-7E08-4C7D-A80F-71F5E9976C60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD443607-5D60-42C8-B3FE-EDAE980D5EBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D49B0F4C-5F9E-467E-8AD9-9E638F42404F}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2682" uniqueCount="444">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2757" uniqueCount="452">
   <si>
     <t>SKU</t>
   </si>
@@ -1385,11 +1385,39 @@
   <si>
     <t>FBAM79351</t>
   </si>
+  <si>
+    <t>FBA79971</t>
+  </si>
+  <si>
+    <t>B0GGHZWMVW</t>
+  </si>
+  <si>
+    <t>SP-01</t>
+  </si>
+  <si>
+    <t>Pipeline</t>
+  </si>
+  <si>
+    <t>FBA79984</t>
+  </si>
+  <si>
+    <t>B0GM1CZC7Y</t>
+  </si>
+  <si>
+    <t>MR-03</t>
+  </si>
+  <si>
+    <t>Open Order</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="164" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
   <fonts count="12">
     <font>
       <sz val="11"/>
@@ -1510,12 +1538,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1547,8 +1576,10 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
+    <cellStyle name="Comma" xfId="3" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="2" xr:uid="{697FC575-8A7C-4715-A8F0-2950C62D8576}"/>
     <cellStyle name="Normal 6" xfId="1" xr:uid="{E5F241CE-C0FC-4730-81C9-F1901EB82A3C}"/>
@@ -1974,7 +2005,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76CBFB1B-DC23-4380-8138-4D6BFF18CBC5}">
-  <dimension ref="A1:L536"/>
+  <dimension ref="A1:L551"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.88671875" style="1" bestFit="1" customWidth="1"/>
@@ -12845,29 +12876,329 @@
       </c>
       <c r="K536" s="8"/>
     </row>
+    <row r="537" spans="1:11" ht="15" customHeight="1">
+      <c r="A537" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B537" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C537" t="s">
+        <v>262</v>
+      </c>
+      <c r="D537" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="I537" s="11">
+        <v>522</v>
+      </c>
+      <c r="J537" s="1" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="538" spans="1:11" ht="15" customHeight="1">
+      <c r="A538" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B538" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C538" t="s">
+        <v>262</v>
+      </c>
+      <c r="D538" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="I538" s="11">
+        <v>1002</v>
+      </c>
+      <c r="J538" s="1" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="539" spans="1:11" ht="15" customHeight="1">
+      <c r="A539" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="B539" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="C539" t="s">
+        <v>262</v>
+      </c>
+      <c r="D539" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="I539" s="11">
+        <v>500</v>
+      </c>
+      <c r="J539" s="1" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="540" spans="1:11" ht="15" customHeight="1">
+      <c r="A540" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B540" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="C540" t="s">
+        <v>262</v>
+      </c>
+      <c r="D540" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="I540" s="1">
+        <v>2000</v>
+      </c>
+      <c r="J540" s="1" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="541" spans="1:11" ht="15" customHeight="1">
+      <c r="A541" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B541" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C541" t="s">
+        <v>262</v>
+      </c>
+      <c r="D541" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="I541" s="1">
+        <v>1472</v>
+      </c>
+      <c r="J541" s="1" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="542" spans="1:11" ht="15" customHeight="1">
+      <c r="A542" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B542" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="C542" t="s">
+        <v>262</v>
+      </c>
+      <c r="D542" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="I542" s="1">
+        <v>2000</v>
+      </c>
+      <c r="J542" s="1" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="543" spans="1:11" ht="15" customHeight="1">
+      <c r="A543" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B543" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C543" t="s">
+        <v>262</v>
+      </c>
+      <c r="D543" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="I543" s="1">
+        <v>1008</v>
+      </c>
+      <c r="J543" s="1" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="544" spans="1:11" ht="15" customHeight="1">
+      <c r="A544" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B544" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C544" t="s">
+        <v>262</v>
+      </c>
+      <c r="D544" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="I544" s="1">
+        <v>2000</v>
+      </c>
+      <c r="J544" s="1" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="545" spans="1:10" ht="15" customHeight="1">
+      <c r="A545" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B545" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="C545" t="s">
+        <v>262</v>
+      </c>
+      <c r="D545" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="I545" s="1">
+        <v>1000</v>
+      </c>
+      <c r="J545" s="1" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="546" spans="1:10" ht="15" customHeight="1">
+      <c r="A546" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B546" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="C546" t="s">
+        <v>262</v>
+      </c>
+      <c r="D546" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="I546" s="1">
+        <v>2000</v>
+      </c>
+      <c r="J546" s="1" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="547" spans="1:10" ht="15" customHeight="1">
+      <c r="A547" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B547" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C547" t="s">
+        <v>262</v>
+      </c>
+      <c r="D547" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="I547" s="1">
+        <v>1000</v>
+      </c>
+      <c r="J547" s="1" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="548" spans="1:10" ht="15" customHeight="1">
+      <c r="A548" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B548" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C548" t="s">
+        <v>262</v>
+      </c>
+      <c r="D548" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="I548" s="1">
+        <v>1000</v>
+      </c>
+      <c r="J548" s="1" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="549" spans="1:10" ht="15" customHeight="1">
+      <c r="A549" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B549" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C549" t="s">
+        <v>262</v>
+      </c>
+      <c r="D549" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="I549" s="1">
+        <v>405</v>
+      </c>
+      <c r="J549" s="1" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="550" spans="1:10" ht="15" customHeight="1">
+      <c r="A550" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="B550" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="C550" t="s">
+        <v>262</v>
+      </c>
+      <c r="D550" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="I550" s="1">
+        <v>504</v>
+      </c>
+      <c r="J550" s="1" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="551" spans="1:10" ht="15" customHeight="1">
+      <c r="A551" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B551" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="C551" t="s">
+        <v>262</v>
+      </c>
+      <c r="D551" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="I551" s="1">
+        <v>200</v>
+      </c>
+      <c r="J551" s="1" t="s">
+        <v>451</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:L536" xr:uid="{76CBFB1B-DC23-4380-8138-4D6BFF18CBC5}"/>
   <phoneticPr fontId="3" type="noConversion"/>
+  <conditionalFormatting sqref="A224:A340">
+    <cfRule type="duplicateValues" dxfId="8" priority="1594"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A328:A330">
+    <cfRule type="duplicateValues" dxfId="7" priority="1591"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="duplicateValues" dxfId="8" priority="1353"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="1353"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:H1">
-    <cfRule type="duplicateValues" dxfId="7" priority="1564"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="1565" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="1564"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="1565" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1">
-    <cfRule type="duplicateValues" dxfId="5" priority="1351"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="1352" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1351"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="1352" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:L1">
-    <cfRule type="duplicateValues" dxfId="3" priority="1349"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="1350" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A328:A330">
-    <cfRule type="duplicateValues" dxfId="1" priority="1591"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A224:A340">
-    <cfRule type="duplicateValues" dxfId="0" priority="1594"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1349"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1350" stopIfTrue="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
